--- a/outputs/programacion_horas.xlsx
+++ b/outputs/programacion_horas.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L161"/>
+  <dimension ref="A1:L160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,12 +545,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -572,10 +572,10 @@
         <v>180</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3" t="inlineStr"/>
     </row>
@@ -593,37 +593,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" t="inlineStr"/>
     </row>
@@ -747,17 +747,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -833,12 +833,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>400CIG037</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -863,7 +863,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L9" t="inlineStr"/>
     </row>
@@ -881,27 +881,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400CIG037</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -911,7 +911,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L10" t="inlineStr"/>
     </row>
@@ -939,17 +939,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -987,17 +987,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1247,7 +1247,7 @@
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L17" t="inlineStr"/>
     </row>
@@ -1265,37 +1265,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L18" t="inlineStr"/>
     </row>
@@ -1323,24 +1323,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_VIERNES</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>120</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
         <v>9</v>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>400CIG037</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1391,7 +1391,7 @@
         <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L20" t="inlineStr"/>
     </row>
@@ -1409,27 +1409,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400CIG037</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1439,7 +1439,7 @@
         <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L21" t="inlineStr"/>
     </row>
@@ -1467,17 +1467,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1515,17 +1515,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1775,7 +1775,7 @@
         <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L28" t="inlineStr"/>
     </row>
@@ -1793,37 +1793,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L29" t="inlineStr"/>
     </row>
@@ -1851,24 +1851,24 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_VIERNES</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I30" t="n">
         <v>120</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
         <v>13</v>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>400CIG037</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1919,7 +1919,7 @@
         <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L31" t="inlineStr"/>
     </row>
@@ -1937,27 +1937,27 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400CIG037</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -1967,7 +1967,7 @@
         <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L32" t="inlineStr"/>
     </row>
@@ -1995,17 +1995,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2043,17 +2043,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2300,10 +2300,10 @@
         <v>180</v>
       </c>
       <c r="J39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L39" t="inlineStr"/>
     </row>
@@ -2321,37 +2321,37 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L40" t="inlineStr"/>
     </row>
@@ -2849,12 +2849,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400CIG029 -3cred- Proyecto de grado I</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400CIG028</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2876,10 +2876,10 @@
         <v>180</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L51" t="inlineStr"/>
     </row>
@@ -2897,12 +2897,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>400CIG029 -3cred- Proyecto de grado I</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>400CIG028</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2945,37 +2945,37 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L53" t="inlineStr"/>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>400CIG037</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3089,27 +3089,27 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400CIG037</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -3147,17 +3147,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -3195,17 +3195,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3452,10 +3452,10 @@
         <v>180</v>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K63" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L63" t="inlineStr"/>
     </row>
@@ -3473,37 +3473,37 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L64" t="inlineStr"/>
     </row>
@@ -3627,17 +3627,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -3675,17 +3675,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -3723,17 +3723,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3980,10 +3980,10 @@
         <v>180</v>
       </c>
       <c r="J74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K74" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L74" t="inlineStr"/>
     </row>
@@ -4001,37 +4001,37 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K75" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L75" t="inlineStr"/>
     </row>
@@ -4155,17 +4155,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -4203,17 +4203,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -4251,17 +4251,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4508,7 +4508,7 @@
         <v>180</v>
       </c>
       <c r="J85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K85" t="n">
         <v>24</v>
@@ -4529,34 +4529,34 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K86" t="n">
         <v>24</v>
@@ -4683,17 +4683,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -4731,17 +4731,17 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -4779,17 +4779,17 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5036,10 +5036,10 @@
         <v>180</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K96" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L96" t="inlineStr"/>
     </row>
@@ -5057,37 +5057,37 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L97" t="inlineStr"/>
     </row>
@@ -5211,17 +5211,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -5259,17 +5259,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I101" t="n">
@@ -5307,17 +5307,17 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -5489,12 +5489,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400CIG029 -3cred- Proyecto de grado I</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400CIG028</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5516,10 +5516,10 @@
         <v>180</v>
       </c>
       <c r="J106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K106" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="L106" t="inlineStr"/>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>400CIG029 -3cred- Proyecto de grado I</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>400CIG028</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5585,37 +5585,37 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K108" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="L108" t="inlineStr"/>
     </row>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5711,7 +5711,7 @@
         <v>3</v>
       </c>
       <c r="K110" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L110" t="inlineStr"/>
     </row>
@@ -5729,27 +5729,27 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -5759,7 +5759,7 @@
         <v>3</v>
       </c>
       <c r="K111" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="L111" t="inlineStr"/>
     </row>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5996,10 +5996,10 @@
         <v>180</v>
       </c>
       <c r="J116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K116" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L116" t="inlineStr"/>
     </row>
@@ -6017,37 +6017,37 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K117" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L117" t="inlineStr"/>
     </row>
@@ -6171,17 +6171,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I120" t="n">
@@ -6219,17 +6219,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -6267,17 +6267,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6524,10 +6524,10 @@
         <v>180</v>
       </c>
       <c r="J127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K127" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L127" t="inlineStr"/>
     </row>
@@ -6545,37 +6545,37 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K128" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L128" t="inlineStr"/>
     </row>
@@ -6699,17 +6699,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -6747,17 +6747,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I132" t="n">
@@ -6795,17 +6795,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I133" t="n">
@@ -6977,12 +6977,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7004,10 +7004,10 @@
         <v>180</v>
       </c>
       <c r="J137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K137" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L137" t="inlineStr"/>
     </row>
@@ -7025,37 +7025,37 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K138" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L138" t="inlineStr"/>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7151,7 +7151,7 @@
         <v>3</v>
       </c>
       <c r="K140" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L140" t="inlineStr"/>
     </row>
@@ -7169,27 +7169,27 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I141" t="n">
@@ -7199,7 +7199,7 @@
         <v>3</v>
       </c>
       <c r="K141" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="L141" t="inlineStr"/>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7244,10 +7244,10 @@
         <v>180</v>
       </c>
       <c r="J142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K142" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L142" t="inlineStr"/>
     </row>
@@ -7265,37 +7265,37 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K143" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="L143" t="inlineStr"/>
     </row>
@@ -7361,12 +7361,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7391,7 +7391,7 @@
         <v>3</v>
       </c>
       <c r="K145" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L145" t="inlineStr"/>
     </row>
@@ -7409,27 +7409,27 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I146" t="n">
@@ -7439,7 +7439,7 @@
         <v>3</v>
       </c>
       <c r="K146" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L146" t="inlineStr"/>
     </row>
@@ -7457,12 +7457,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7484,10 +7484,10 @@
         <v>180</v>
       </c>
       <c r="J147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K147" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L147" t="inlineStr"/>
     </row>
@@ -7505,37 +7505,37 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K148" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L148" t="inlineStr"/>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7724,10 +7724,10 @@
         <v>180</v>
       </c>
       <c r="J152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K152" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="L152" t="inlineStr"/>
     </row>
@@ -7745,37 +7745,37 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K153" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="L153" t="inlineStr"/>
     </row>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7871,7 +7871,7 @@
         <v>3</v>
       </c>
       <c r="K155" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L155" t="inlineStr"/>
     </row>
@@ -7889,27 +7889,27 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I156" t="n">
@@ -7919,7 +7919,7 @@
         <v>3</v>
       </c>
       <c r="K156" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L156" t="inlineStr"/>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -8063,7 +8063,7 @@
         <v>3</v>
       </c>
       <c r="K159" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L159" t="inlineStr"/>
     </row>
@@ -8091,77 +8091,29 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I160" t="n">
         <v>180</v>
       </c>
       <c r="J160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K160" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>19</v>
-      </c>
-      <c r="B161" s="1" t="n">
-        <v>46361</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>sabado</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>400CIS002</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>FRANJA_DOS_SABADO</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>13:00:00</t>
-        </is>
-      </c>
-      <c r="I161" t="n">
-        <v>180</v>
-      </c>
-      <c r="J161" t="n">
-        <v>1</v>
-      </c>
-      <c r="K161" t="n">
-        <v>46</v>
-      </c>
-      <c r="L161" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8429,20 +8381,20 @@
         <v>48</v>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H7" t="n">
         <v>15</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Completa</t>
+          <t>Incompleta — faltan 3.0h</t>
         </is>
       </c>
     </row>

--- a/outputs/programacion_horas.xlsx
+++ b/outputs/programacion_horas.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L160"/>
+  <dimension ref="A1:L161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,82 +1013,82 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>miercoles</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400CIG029 -4cred- Proyecto de grado 2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400CIG029</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_SABADO</t>
+          <t>FRANJA_UNO_MIERCOLES</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400CIG029 -3cred- Proyecto de grado I</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400CIG028</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FRANJA_CUATRO_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L14" t="inlineStr"/>
     </row>
@@ -1112,46 +1112,46 @@
         <v>3</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>miercoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>400CIG029 -4cred- Proyecto de grado 2</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>400CIG029</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_MIERCOLES</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L15" t="inlineStr"/>
     </row>
@@ -1169,37 +1169,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>400CIG029 -3cred- Proyecto de grado I</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>400CIG028</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L16" t="inlineStr"/>
     </row>
@@ -1217,37 +1217,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L17" t="inlineStr"/>
     </row>
@@ -1256,46 +1256,46 @@
         <v>3</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_VIERNES</t>
+          <t>FRANJA_UNO_SABADO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L18" t="inlineStr"/>
     </row>
@@ -1304,46 +1304,46 @@
         <v>3</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400CIG037</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L19" t="inlineStr"/>
     </row>
@@ -1361,27 +1361,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400ITA003</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1391,7 +1391,7 @@
         <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L20" t="inlineStr"/>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
+          <t>400ITA005 - 3cred - El Negocio del sw</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>400CIG037</t>
+          <t>400ITA005</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1457,37 +1457,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>400ITA003</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_TRES_SABADO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L22" t="inlineStr"/>
     </row>
@@ -1505,118 +1505,118 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>400ITA005 - 3cred - El Negocio del sw</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>400ITA005</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_CUATRO_SABADO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46249</v>
+        <v>46253</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>miercoles</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400CIG029 -4cred- Proyecto de grado 2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400CIG029</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_SABADO</t>
+          <t>FRANJA_UNO_MIERCOLES</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K24" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46249</v>
+        <v>46255</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400CIG029 -3cred- Proyecto de grado I</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400CIG028</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FRANJA_CUATRO_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L25" t="inlineStr"/>
     </row>
@@ -1640,46 +1640,46 @@
         <v>4</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>miercoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>400CIG029 -4cred- Proyecto de grado 2</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>400CIG029</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_MIERCOLES</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="J26" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="L26" t="inlineStr"/>
     </row>
@@ -1697,37 +1697,37 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>400CIG029 -3cred- Proyecto de grado I</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>400CIG028</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L27" t="inlineStr"/>
     </row>
@@ -1745,37 +1745,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L28" t="inlineStr"/>
     </row>
@@ -1784,46 +1784,46 @@
         <v>4</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_VIERNES</t>
+          <t>FRANJA_UNO_SABADO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L29" t="inlineStr"/>
     </row>
@@ -1832,46 +1832,46 @@
         <v>4</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400CIG037</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L30" t="inlineStr"/>
     </row>
@@ -1889,27 +1889,27 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400ITA003</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -1919,7 +1919,7 @@
         <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L31" t="inlineStr"/>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
+          <t>400ITA005 - 3cred - El Negocio del sw</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>400CIG037</t>
+          <t>400ITA005</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1985,37 +1985,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>400ITA003</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_TRES_SABADO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L33" t="inlineStr"/>
     </row>
@@ -2033,118 +2033,118 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>400ITA005 - 3cred - El Negocio del sw</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>400ITA005</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_CUATRO_SABADO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46256</v>
+        <v>46262</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400CIG029 -3cred- Proyecto de grado I</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400CIG028</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46256</v>
+        <v>46262</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FRANJA_CUATRO_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" t="n">
         <v>12</v>
@@ -2168,46 +2168,46 @@
         <v>5</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>miercoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>400CIG029 -4cred- Proyecto de grado 2</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>400CIG029</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_MIERCOLES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J37" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K37" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L37" t="inlineStr"/>
     </row>
@@ -2225,37 +2225,37 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>400CIG029 -3cred- Proyecto de grado I</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>400CIG028</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L38" t="inlineStr"/>
     </row>
@@ -2264,36 +2264,36 @@
         <v>5</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIG037</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_UNO_SABADO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2312,46 +2312,46 @@
         <v>5</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400ITA003</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_VIERNES</t>
+          <t>FRANJA_UNO_SABADO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L40" t="inlineStr"/>
     </row>
@@ -2360,46 +2360,46 @@
         <v>5</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400ITA005 - 3cred - El Negocio del sw</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400ITA005</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_VIERNES</t>
+          <t>FRANJA_UNO_SABADO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L41" t="inlineStr"/>
     </row>
@@ -2427,17 +2427,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2447,7 +2447,7 @@
         <v>3</v>
       </c>
       <c r="K42" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L42" t="inlineStr"/>
     </row>
@@ -2475,17 +2475,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2495,7 +2495,7 @@
         <v>3</v>
       </c>
       <c r="K43" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L43" t="inlineStr"/>
     </row>
@@ -2523,17 +2523,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -2543,7 +2543,7 @@
         <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L44" t="inlineStr"/>
     </row>
@@ -2561,37 +2561,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>400CIG037</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_TRES_SABADO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L45" t="inlineStr"/>
     </row>
@@ -2609,166 +2609,166 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>400ITA003</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_CUATRO_SABADO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46263</v>
+        <v>46267</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>miercoles</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>400ITA005 - 3cred - El Negocio del sw</t>
+          <t>400CIG029 -4cred- Proyecto de grado 2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>400ITA005</t>
+          <t>400CIG029</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_UNO_MIERCOLES</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K47" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46263</v>
+        <v>46269</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400CIG029 -3cred- Proyecto de grado I</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400CIG028</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46263</v>
+        <v>46269</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FRANJA_CUATRO_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L49" t="inlineStr"/>
     </row>
@@ -2792,46 +2792,46 @@
         <v>6</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>miercoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>400CIG029 -4cred- Proyecto de grado 2</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>400CIG029</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_MIERCOLES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J50" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="L50" t="inlineStr"/>
     </row>
@@ -2849,37 +2849,37 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>400CIG029 -3cred- Proyecto de grado I</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>400CIG028</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L51" t="inlineStr"/>
     </row>
@@ -2888,36 +2888,36 @@
         <v>6</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_UNO_SABADO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -2927,7 +2927,7 @@
         <v>3</v>
       </c>
       <c r="K52" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L52" t="inlineStr"/>
     </row>
@@ -2936,46 +2936,46 @@
         <v>6</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400CIG037</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L53" t="inlineStr"/>
     </row>
@@ -2984,43 +2984,43 @@
         <v>6</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400ITA003</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K54" t="n">
         <v>18</v>
@@ -3041,27 +3041,27 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400ITA005 - 3cred - El Negocio del sw</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400ITA005</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -3089,37 +3089,37 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>400CIG037</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_TRES_SABADO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L56" t="inlineStr"/>
     </row>
@@ -3137,130 +3137,130 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>400ITA003</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_CUATRO_SABADO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K57" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>miercoles</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>400ITA005 - 3cred - El Negocio del sw</t>
+          <t>400CIG029 -4cred- Proyecto de grado 2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>400ITA005</t>
+          <t>400CIG029</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_UNO_MIERCOLES</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="J58" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K58" t="n">
-        <v>18</v>
+        <v>7.5</v>
       </c>
       <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400CIG029 -3cred- Proyecto de grado I</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400CIG028</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K59" t="n">
         <v>18</v>
@@ -3269,34 +3269,34 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FRANJA_CUATRO_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K60" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L60" t="inlineStr"/>
     </row>
@@ -3320,46 +3320,46 @@
         <v>7</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>miercoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>400CIG029 -4cred- Proyecto de grado 2</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>400CIG029</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_MIERCOLES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J61" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="L61" t="inlineStr"/>
     </row>
@@ -3377,37 +3377,37 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>400CIG029 -3cred- Proyecto de grado I</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>400CIG028</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L62" t="inlineStr"/>
     </row>
@@ -3416,36 +3416,36 @@
         <v>7</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_UNO_SABADO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -3455,7 +3455,7 @@
         <v>3</v>
       </c>
       <c r="K63" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="L63" t="inlineStr"/>
     </row>
@@ -3464,46 +3464,46 @@
         <v>7</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400CIG037</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K64" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L64" t="inlineStr"/>
     </row>
@@ -3512,46 +3512,46 @@
         <v>7</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400ITA003</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L65" t="inlineStr"/>
     </row>
@@ -3569,27 +3569,27 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400ITA005 - 3cred - El Negocio del sw</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400ITA005</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -3599,7 +3599,7 @@
         <v>3</v>
       </c>
       <c r="K66" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="L66" t="inlineStr"/>
     </row>
@@ -3617,37 +3617,37 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>400CIG037</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_TRES_SABADO</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L67" t="inlineStr"/>
     </row>
@@ -3665,166 +3665,166 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>400ITA003</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_CUATRO_SABADO</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>46277</v>
+        <v>46288</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>miercoles</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>400ITA005 - 3cred - El Negocio del sw</t>
+          <t>400CIG029 -4cred- Proyecto de grado 2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>400ITA005</t>
+          <t>400CIG029</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_UNO_MIERCOLES</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="J69" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K69" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>46277</v>
+        <v>46290</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400CIG029 -3cred- Proyecto de grado I</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400CIG028</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K70" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46277</v>
+        <v>46290</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FRANJA_CUATRO_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3833,13 +3833,13 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K71" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L71" t="inlineStr"/>
     </row>
@@ -3848,46 +3848,46 @@
         <v>9</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>miercoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>400CIG029 -4cred- Proyecto de grado 2</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>400CIG029</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_MIERCOLES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J72" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K72" t="n">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="L72" t="inlineStr"/>
     </row>
@@ -3905,37 +3905,37 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>400CIG029 -3cred- Proyecto de grado I</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>400CIG028</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K73" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L73" t="inlineStr"/>
     </row>
@@ -3944,36 +3944,36 @@
         <v>9</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_UNO_SABADO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -3983,7 +3983,7 @@
         <v>3</v>
       </c>
       <c r="K74" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="L74" t="inlineStr"/>
     </row>
@@ -3992,46 +3992,46 @@
         <v>9</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400CIG037</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K75" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L75" t="inlineStr"/>
     </row>
@@ -4040,46 +4040,46 @@
         <v>9</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400ITA003</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K76" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L76" t="inlineStr"/>
     </row>
@@ -4097,27 +4097,27 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400ITA005 - 3cred - El Negocio del sw</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400ITA005</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -4127,7 +4127,7 @@
         <v>3</v>
       </c>
       <c r="K77" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L77" t="inlineStr"/>
     </row>
@@ -4145,37 +4145,37 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>400CIG037</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_TRES_SABADO</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K78" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L78" t="inlineStr"/>
     </row>
@@ -4193,34 +4193,34 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>400ITA003</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_CUATRO_SABADO</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K79" t="n">
         <v>24</v>
@@ -4229,130 +4229,130 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>miercoles</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>400ITA005 - 3cred - El Negocio del sw</t>
+          <t>400CIG029 -4cred- Proyecto de grado 2</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>400ITA005</t>
+          <t>400CIG029</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_UNO_MIERCOLES</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="J80" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K80" t="n">
-        <v>24</v>
+        <v>10.5</v>
       </c>
       <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46291</v>
+        <v>46297</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400CIG029 -3cred- Proyecto de grado I</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400CIG028</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K81" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46291</v>
+        <v>46297</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FRANJA_CUATRO_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4361,13 +4361,13 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K82" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L82" t="inlineStr"/>
     </row>
@@ -4376,46 +4376,46 @@
         <v>10</v>
       </c>
       <c r="B83" s="1" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>miercoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>400CIG029 -4cred- Proyecto de grado 2</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>400CIG029</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_MIERCOLES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J83" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K83" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L83" t="inlineStr"/>
     </row>
@@ -4433,34 +4433,34 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>400CIG029 -3cred- Proyecto de grado I</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>400CIG028</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K84" t="n">
         <v>24</v>
@@ -4472,36 +4472,36 @@
         <v>10</v>
       </c>
       <c r="B85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_UNO_SABADO</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -4511,7 +4511,7 @@
         <v>3</v>
       </c>
       <c r="K85" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="L85" t="inlineStr"/>
     </row>
@@ -4520,46 +4520,46 @@
         <v>10</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400CIG037</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K86" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L86" t="inlineStr"/>
     </row>
@@ -4568,46 +4568,46 @@
         <v>10</v>
       </c>
       <c r="B87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400ITA003</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K87" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L87" t="inlineStr"/>
     </row>
@@ -4625,27 +4625,27 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400ITA005 - 3cred - El Negocio del sw</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400ITA005</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -4655,7 +4655,7 @@
         <v>3</v>
       </c>
       <c r="K88" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="L88" t="inlineStr"/>
     </row>
@@ -4673,37 +4673,37 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>400CIG037</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_TRES_SABADO</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K89" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L89" t="inlineStr"/>
     </row>
@@ -4721,166 +4721,166 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>400ITA003</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_CUATRO_SABADO</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K90" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>miercoles</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>400ITA005 - 3cred - El Negocio del sw</t>
+          <t>400CIG029 -4cred- Proyecto de grado 2</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>400ITA005</t>
+          <t>400CIG029</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_UNO_MIERCOLES</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="J91" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K91" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46298</v>
+        <v>46304</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400CIG029 -3cred- Proyecto de grado I</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400CIG028</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K92" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46298</v>
+        <v>46304</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FRANJA_CUATRO_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4889,13 +4889,13 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K93" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L93" t="inlineStr"/>
     </row>
@@ -4904,46 +4904,46 @@
         <v>11</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>miercoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>400CIG029 -4cred- Proyecto de grado 2</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>400CIG029</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_MIERCOLES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J94" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>13.5</v>
+        <v>26</v>
       </c>
       <c r="L94" t="inlineStr"/>
     </row>
@@ -4961,37 +4961,37 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>400CIG029 -3cred- Proyecto de grado I</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>400CIG028</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K95" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L95" t="inlineStr"/>
     </row>
@@ -5000,36 +5000,36 @@
         <v>11</v>
       </c>
       <c r="B96" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_UNO_SABADO</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -5039,7 +5039,7 @@
         <v>3</v>
       </c>
       <c r="K96" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="L96" t="inlineStr"/>
     </row>
@@ -5048,46 +5048,46 @@
         <v>11</v>
       </c>
       <c r="B97" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400CIG037</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K97" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L97" t="inlineStr"/>
     </row>
@@ -5096,46 +5096,46 @@
         <v>11</v>
       </c>
       <c r="B98" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400ITA003</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K98" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L98" t="inlineStr"/>
     </row>
@@ -5153,27 +5153,27 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400ITA005 - 3cred - El Negocio del sw</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400ITA005</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -5183,7 +5183,7 @@
         <v>3</v>
       </c>
       <c r="K99" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="L99" t="inlineStr"/>
     </row>
@@ -5201,34 +5201,34 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>400CIG037</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_TRES_SABADO</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K100" t="n">
         <v>30</v>
@@ -5249,75 +5249,75 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>400ITA003</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_CUATRO_SABADO</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K101" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B102" s="1" t="n">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>400ITA005 - 3cred - El Negocio del sw</t>
+          <t>400CIG029 -3cred- Proyecto de grado I</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>400ITA005</t>
+          <t>400CIG028</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -5333,87 +5333,87 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B103" s="1" t="n">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K103" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B104" s="1" t="n">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FRANJA_CUATRO_SABADO</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -5423,7 +5423,7 @@
         <v>2</v>
       </c>
       <c r="K104" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="L104" t="inlineStr"/>
     </row>
@@ -5432,46 +5432,46 @@
         <v>12</v>
       </c>
       <c r="B105" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>miercoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>400CIG029 -4cred- Proyecto de grado 2</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>400CIG029</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_MIERCOLES</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J105" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K105" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="L105" t="inlineStr"/>
     </row>
@@ -5480,36 +5480,36 @@
         <v>12</v>
       </c>
       <c r="B106" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>400CIG029 -3cred- Proyecto de grado I</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>400CIG028</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_UNO_SABADO</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -5519,7 +5519,7 @@
         <v>3</v>
       </c>
       <c r="K106" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L106" t="inlineStr"/>
     </row>
@@ -5528,36 +5528,36 @@
         <v>12</v>
       </c>
       <c r="B107" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -5567,7 +5567,7 @@
         <v>3</v>
       </c>
       <c r="K107" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="L107" t="inlineStr"/>
     </row>
@@ -5576,36 +5576,36 @@
         <v>12</v>
       </c>
       <c r="B108" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_VIERNES</t>
+          <t>FRANJA_TRES_SABADO</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -5615,7 +5615,7 @@
         <v>2</v>
       </c>
       <c r="K108" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="L108" t="inlineStr"/>
     </row>
@@ -5624,36 +5624,36 @@
         <v>12</v>
       </c>
       <c r="B109" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_VIERNES</t>
+          <t>FRANJA_CUATRO_SABADO</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -5663,93 +5663,93 @@
         <v>2</v>
       </c>
       <c r="K109" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B110" s="1" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>miercoles</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400CIG029 -4cred- Proyecto de grado 2</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400CIG029</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_UNO_MIERCOLES</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="J110" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K110" t="n">
-        <v>29</v>
+        <v>13.5</v>
       </c>
       <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B111" s="1" t="n">
-        <v>46312</v>
+        <v>46318</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400CIG029 -3cred- Proyecto de grado I</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400CIG028</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -5759,93 +5759,93 @@
         <v>3</v>
       </c>
       <c r="K111" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="L111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B112" s="1" t="n">
-        <v>46312</v>
+        <v>46318</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K112" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="L112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B113" s="1" t="n">
-        <v>46312</v>
+        <v>46318</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FRANJA_CUATRO_SABADO</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -5855,7 +5855,7 @@
         <v>2</v>
       </c>
       <c r="K113" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="L113" t="inlineStr"/>
     </row>
@@ -5864,46 +5864,46 @@
         <v>13</v>
       </c>
       <c r="B114" s="1" t="n">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>miercoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>400CIG029 -4cred- Proyecto de grado 2</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>400CIG029</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_MIERCOLES</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J114" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K114" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="L114" t="inlineStr"/>
     </row>
@@ -5912,36 +5912,36 @@
         <v>13</v>
       </c>
       <c r="B115" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>400CIG029 -3cred- Proyecto de grado I</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>400CIG028</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_UNO_SABADO</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -5951,7 +5951,7 @@
         <v>3</v>
       </c>
       <c r="K115" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="L115" t="inlineStr"/>
     </row>
@@ -5960,36 +5960,36 @@
         <v>13</v>
       </c>
       <c r="B116" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIG037</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -6008,46 +6008,46 @@
         <v>13</v>
       </c>
       <c r="B117" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400ITA003</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K117" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L117" t="inlineStr"/>
     </row>
@@ -6056,46 +6056,46 @@
         <v>13</v>
       </c>
       <c r="B118" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400ITA005 - 3cred - El Negocio del sw</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400ITA005</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K118" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L118" t="inlineStr"/>
     </row>
@@ -6113,37 +6113,37 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_TRES_SABADO</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K119" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="L119" t="inlineStr"/>
     </row>
@@ -6161,123 +6161,123 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>400CIG037</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_CUATRO_SABADO</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K120" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B121" s="1" t="n">
-        <v>46319</v>
+        <v>46323</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>miercoles</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
+          <t>400CIG029 -4cred- Proyecto de grado 2</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>400ITA003</t>
+          <t>400CIG029</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_UNO_MIERCOLES</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="J121" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K121" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="L121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B122" s="1" t="n">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>400ITA005 - 3cred - El Negocio del sw</t>
+          <t>400CIG029 -3cred- Proyecto de grado I</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>400ITA005</t>
+          <t>400CIG028</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -6287,93 +6287,93 @@
         <v>3</v>
       </c>
       <c r="K122" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B123" s="1" t="n">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K123" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B124" s="1" t="n">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FRANJA_CUATRO_SABADO</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -6383,7 +6383,7 @@
         <v>2</v>
       </c>
       <c r="K124" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="L124" t="inlineStr"/>
     </row>
@@ -6392,46 +6392,46 @@
         <v>14</v>
       </c>
       <c r="B125" s="1" t="n">
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>miercoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>400CIG029 -4cred- Proyecto de grado 2</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>400CIG029</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_MIERCOLES</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J125" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K125" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="L125" t="inlineStr"/>
     </row>
@@ -6440,36 +6440,36 @@
         <v>14</v>
       </c>
       <c r="B126" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>400CIG029 -3cred- Proyecto de grado I</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>400CIG028</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_UNO_SABADO</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -6479,7 +6479,7 @@
         <v>3</v>
       </c>
       <c r="K126" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="L126" t="inlineStr"/>
     </row>
@@ -6488,36 +6488,36 @@
         <v>14</v>
       </c>
       <c r="B127" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIG037</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I127" t="n">
@@ -6536,46 +6536,46 @@
         <v>14</v>
       </c>
       <c r="B128" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400ITA003</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K128" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L128" t="inlineStr"/>
     </row>
@@ -6584,46 +6584,46 @@
         <v>14</v>
       </c>
       <c r="B129" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400ITA005 - 3cred - El Negocio del sw</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400ITA005</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K129" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L129" t="inlineStr"/>
     </row>
@@ -6641,37 +6641,37 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_TRES_SABADO</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="L130" t="inlineStr"/>
     </row>
@@ -6689,75 +6689,75 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>400CIG037 -3cred -Tópicos Avanzados Ing de Software</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>400CIG037</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_CUATRO_SABADO</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K131" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="L131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B132" s="1" t="n">
-        <v>46326</v>
+        <v>46332</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>400ITA003 - 3cred - Arquitectura de Software en la nube</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>400ITA003</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I132" t="n">
@@ -6767,93 +6767,93 @@
         <v>3</v>
       </c>
       <c r="K132" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B133" s="1" t="n">
-        <v>46326</v>
+        <v>46332</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>400ITA005 - 3cred - El Negocio del sw</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>400ITA005</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K133" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="L133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B134" s="1" t="n">
-        <v>46326</v>
+        <v>46332</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_SABADO</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -6863,16 +6863,16 @@
         <v>2</v>
       </c>
       <c r="K134" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="L134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B135" s="1" t="n">
-        <v>46326</v>
+        <v>46333</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -6881,37 +6881,37 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>400ITA007</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FRANJA_CUATRO_SABADO</t>
+          <t>FRANJA_UNO_SABADO</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K135" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="L135" t="inlineStr"/>
     </row>
@@ -6920,46 +6920,46 @@
         <v>15</v>
       </c>
       <c r="B136" s="1" t="n">
-        <v>46330</v>
+        <v>46333</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>miercoles</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>400CIG029 -4cred- Proyecto de grado 2</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>400CIG029</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_MIERCOLES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="J136" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="K136" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="L136" t="inlineStr"/>
     </row>
@@ -6968,46 +6968,46 @@
         <v>15</v>
       </c>
       <c r="B137" s="1" t="n">
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_TRES_SABADO</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K137" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L137" t="inlineStr"/>
     </row>
@@ -7016,36 +7016,36 @@
         <v>15</v>
       </c>
       <c r="B138" s="1" t="n">
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400ITA007 - 4cred- Desarrollo de Software seguro</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400ITA007</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_VIERNES</t>
+          <t>FRANJA_CUATRO_SABADO</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
           <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
         </is>
       </c>
       <c r="I138" t="n">
@@ -7055,93 +7055,93 @@
         <v>2</v>
       </c>
       <c r="K138" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="L138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B139" s="1" t="n">
-        <v>46332</v>
+        <v>46337</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>miercoles</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400CIG029 -4cred- Proyecto de grado 2</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400CIG029</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_VIERNES</t>
+          <t>FRANJA_UNO_MIERCOLES</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J139" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K139" t="n">
-        <v>34</v>
+        <v>16.5</v>
       </c>
       <c r="L139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B140" s="1" t="n">
-        <v>46333</v>
+        <v>46339</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I140" t="n">
@@ -7151,20 +7151,20 @@
         <v>3</v>
       </c>
       <c r="K140" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B141" s="1" t="n">
-        <v>46333</v>
+        <v>46339</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7179,27 +7179,27 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K141" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L141" t="inlineStr"/>
     </row>
@@ -7217,37 +7217,37 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K142" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L142" t="inlineStr"/>
     </row>
@@ -7256,46 +7256,46 @@
         <v>16</v>
       </c>
       <c r="B143" s="1" t="n">
-        <v>46339</v>
+        <v>46340</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_VIERNES</t>
+          <t>FRANJA_UNO_SABADO</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K143" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L143" t="inlineStr"/>
     </row>
@@ -7304,132 +7304,132 @@
         <v>16</v>
       </c>
       <c r="B144" s="1" t="n">
-        <v>46339</v>
+        <v>46340</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_VIERNES</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K144" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B145" s="1" t="n">
-        <v>46340</v>
+        <v>46344</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>miercoles</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400CIG029 -4cred- Proyecto de grado 2</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400CIG029</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_UNO_MIERCOLES</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="J145" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K145" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="L145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B146" s="1" t="n">
-        <v>46340</v>
+        <v>46346</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400FTA005</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I146" t="n">
@@ -7439,7 +7439,7 @@
         <v>3</v>
       </c>
       <c r="K146" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L146" t="inlineStr"/>
     </row>
@@ -7457,37 +7457,37 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>400FTA005 -3cred- Ética e Impactos de la Tecnol</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>400FTA005</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_DOS_VIERNES</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K147" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L147" t="inlineStr"/>
     </row>
@@ -7505,27 +7505,27 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400CIS002</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_VIERNES</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -7535,7 +7535,7 @@
         <v>2</v>
       </c>
       <c r="K148" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L148" t="inlineStr"/>
     </row>
@@ -7544,46 +7544,46 @@
         <v>17</v>
       </c>
       <c r="B149" s="1" t="n">
-        <v>46346</v>
+        <v>46347</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sabado</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400CIS021</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_VIERNES</t>
+          <t>FRANJA_UNO_SABADO</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K149" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L149" t="inlineStr"/>
     </row>
@@ -7611,17 +7611,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -7631,55 +7631,55 @@
         <v>3</v>
       </c>
       <c r="K150" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B151" s="1" t="n">
-        <v>46347</v>
+        <v>46351</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>miercoles</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>400CIS021 - 4cred- Ingeniería de Requerimientos</t>
+          <t>400CIG029 -4cred- Proyecto de grado 2</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>400CIS021</t>
+          <t>400CIG029</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>FRANJA_DOS_SABADO</t>
+          <t>FRANJA_UNO_MIERCOLES</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="J151" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K151" t="n">
-        <v>45</v>
+        <v>19.5</v>
       </c>
       <c r="L151" t="inlineStr"/>
     </row>
@@ -7928,46 +7928,46 @@
         <v>19</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>46360</v>
+        <v>46358</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>miercoles</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
+          <t>400CIG029 -4cred- Proyecto de grado 2</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>400CID002</t>
+          <t>400CIG029</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_VIERNES</t>
+          <t>FRANJA_UNO_MIERCOLES</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="J157" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K157" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L157" t="inlineStr"/>
     </row>
@@ -7985,37 +7985,37 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>400CIS002 - 4cred- Arquitectura de software</t>
+          <t>400CID002 - 4cred- Sistemas de Bases de Datos</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>400CIS002</t>
+          <t>400CID002</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>FRANJA_TRES_VIERNES</t>
+          <t>FRANJA_UNO_VIERNES</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K158" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L158" t="inlineStr"/>
     </row>
@@ -8024,11 +8024,11 @@
         <v>19</v>
       </c>
       <c r="B159" s="1" t="n">
-        <v>46361</v>
+        <v>46360</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>sabado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8043,27 +8043,27 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>FRANJA_UNO_SABADO</t>
+          <t>FRANJA_TRES_VIERNES</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K159" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="L159" t="inlineStr"/>
     </row>
@@ -8091,29 +8091,77 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
+          <t>FRANJA_UNO_SABADO</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>07:00:00</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>180</v>
+      </c>
+      <c r="J160" t="n">
+        <v>3</v>
+      </c>
+      <c r="K160" t="n">
+        <v>45</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>19</v>
+      </c>
+      <c r="B161" s="1" t="n">
+        <v>46361</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>sabado</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>400CIS002 - 4cred- Arquitectura de software</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>400CIS002</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
           <t>FRANJA_DOS_SABADO</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
+      <c r="H161" t="inlineStr">
         <is>
           <t>13:00:00</t>
         </is>
       </c>
-      <c r="I160" t="n">
-        <v>180</v>
-      </c>
-      <c r="J160" t="n">
+      <c r="I161" t="n">
+        <v>180</v>
+      </c>
+      <c r="J161" t="n">
         <v>1</v>
       </c>
-      <c r="K160" t="n">
+      <c r="K161" t="n">
         <v>46</v>
       </c>
-      <c r="L160" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8526,23 +8574,23 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
         <v>8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Incompleta — faltan 0.5h</t>
+          <t>Completa</t>
         </is>
       </c>
     </row>
